--- a/labs/lab-02-generate-and-verify-formula-columns-and-lookups-for-job-requisitions/data/BrightPath_Job_Requisitions.xlsx
+++ b/labs/lab-02-generate-and-verify-formula-columns-and-lookups-for-job-requisitions/data/BrightPath_Job_Requisitions.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -81,6 +81,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3906,12 +3909,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -3949,7 +3952,369 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>In tblRequisitions, add a column Recruiter_Name that looks up Recruiter_Name from tblRecruiters using Recruiter_ID. Use XLOOKUP and return "Not found" if there is no match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Explain the Recruiter_Name formula, and show one row's Recruiter_ID and Recruiter_Name next to the matching row in tblRecruiters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>3 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Days_Open to tblRequisitions. If Close_Date is blank, use Control!B1 minus Open_Date; otherwise use Close_Date minus Open_Date. Show whole numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>3 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Show one open requisition (blank Close_Date) and one closed requisition with Open_Date, Close_Date and Days_Open, and the subtraction behind each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>4 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Fill_Rate = Filled divided by Openings, formatted as a percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>4 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Est_Fee = Filled x Monthly_Salary_Budget x 12 x Fee_Rate, formatted as S$ with no decimals. Explain the formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Show the Est_Fee calculation for JOB-2002 step by step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>5 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Ageing_Flag that shows "Overdue" when Status is "Open" and Days_Open is greater than 45, otherwise leave it blank. Highlight rows where Ageing_Flag is "Overdue" with a light amber fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>5 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>How many rows have Ageing_Flag = "Overdue"?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>6 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Enter these labels and formulas on the Control sheet exactly as written. Then tell me each result and whether each pair (B3 and B4, B6 and B7) matches:
+A3 Total Est_Fee (column)       B3 =SUM(tblRequisitions[Est_Fee])
+A4 Total fee (independent)      B4 =SUMPRODUCT(tblRequisitions[Filled],tblRequisitions[Monthly_Salary_Budget],tblRequisitions[Fee_Rate])*12
+A5 Avg days to fill (Filled)    B5 =AVERAGEIFS(tblRequisitions[Days_Open],tblRequisitions[Status],"Filled")
+A6 Overdue (independent)        B6 =COUNTIFS(tblRequisitions[Status],"Open",tblRequisitions[Days_Open],"&gt;45")
+A7 Overdue flags (column)       B7 =COUNTIF(tblRequisitions[Ageing_Flag],"Overdue")</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>7 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Using tblRequisitions, which Recruiter_Name has the highest total Est_Fee? Show the total for every recruiter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>7 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>On the Control sheet, add this check for the top recruiter and tell me if it matches your answer:
+=SUMIFS(tblRequisitions[Est_Fee],tblRequisitions[Recruiter_Name],"&lt;name&gt;")</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>7 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Recruiter_Name that looks up Recruiter_Name from tblRecruiters using Recruiter_ID with XLOOKUP. Return "Not found" if missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Days_Open: if Close_Date is blank use Control!B1 minus Open_Date, otherwise Close_Date minus Open_Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Fill_Rate = Filled / Openings formatted as a percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Est_Fee = Filled x Monthly_Salary_Budget x 12 x Fee_Rate, formatted as S$ with no decimals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Add a column Ageing_Flag that shows "Overdue" when Status is Open and Days_Open &gt; 45, otherwise blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Explain the formula in the selected cell step by step, and tell me how blanks are handled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Add a total row to tblRequisitions that sums Openings, Filled and Est_Fee and averages Days_Open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Which recruiter has the highest total Est_Fee? Show every recruiter's total, highest first.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
